--- a/ex/Book1.xlsx
+++ b/ex/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Project\ex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Graph\ex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C5F502-6F01-4A41-8B2B-BEAEC1CB2B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7303468A-955E-43D1-A52E-23893EDC1CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6C18F03-564A-40AA-A193-15F4CED7891A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D6C18F03-564A-40AA-A193-15F4CED7891A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Customer</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>ข้างล่างให้โชว์ข้อมูลในตาม format ใน Excel ที่ทำเป็นตัวอย่างให้ดู</t>
+  </si>
+  <si>
+    <t>ใน Dispatch Monthly History และ 7-Day Dispatch Trend ให้ใช้กราฟตามที่ฉันกำหนด</t>
+  </si>
+  <si>
+    <t>กำหนดให้มี2ประเภทใน1กราฟ กราฟที่1กราฟเส้นไว้แสดงข้อมูลยอดออเดอร์ทั้งหมดที่ต้องส่ง กราฟที่2กราฟ History ไว้แสดงข้อมูลที่ส่งออเดอร์ไปแล้ว</t>
   </si>
 </sst>
 </file>
@@ -536,7 +542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D112A3-4556-4801-AFA6-A8202F895812}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
@@ -549,6 +555,16 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ex/Book1.xlsx
+++ b/ex/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Graph\ex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7303468A-955E-43D1-A52E-23893EDC1CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A532CED-6521-4517-A0DA-EC1B12938E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D6C18F03-564A-40AA-A193-15F4CED7891A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Customer</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>กำหนดให้มี2ประเภทใน1กราฟ กราฟที่1กราฟเส้นไว้แสดงข้อมูลยอดออเดอร์ทั้งหมดที่ต้องส่ง กราฟที่2กราฟ History ไว้แสดงข้อมูลที่ส่งออเดอร์ไปแล้ว</t>
+  </si>
+  <si>
+    <t>ส่วนกราฟDelay รายวัน (7 วัน)ให้เปลี่ยนเป็น History โชว์ว่าออเดอร์ไหนค้างส่งมากที่สุดเรียงจากมากไปน้อยและมีกี่ชิ้น</t>
   </si>
 </sst>
 </file>
@@ -542,7 +545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D112A3-4556-4801-AFA6-A8202F895812}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
@@ -565,6 +568,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
